--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR LIBANORI FEDERICO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR LIBANORI FEDERICO.xlsx
@@ -684,13 +684,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>392</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>79</v>
@@ -863,7 +863,7 @@
         <v>81</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>24</v>
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>20</v>
@@ -922,7 +922,7 @@
         <v>13</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>1</v>
@@ -972,7 +972,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>9</v>
@@ -981,7 +981,7 @@
         <v>20</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>0</v>
